--- a/exports/colleges/25366_nalsar-university-of-law-nalsar-hyderabad.xlsx
+++ b/exports/colleges/25366_nalsar-university-of-law-nalsar-hyderabad.xlsx
@@ -445,7 +445,7 @@
     <col width="53" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="158" customWidth="1" min="13" max="13"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>CD Rank #12</t>
+          <t>Rank #2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -605,11 +605,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="86" customWidth="1" min="3" max="3"/>
     <col width="86" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -617,7 +617,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -692,7 +692,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Master of Laws [L.L.M]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.75 Lakhs</t>
+          <t>1.75 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LLB + CLAT-PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CLAT PG</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 Dec - 27 Dec 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.79 Lakhs</t>
+          <t>8.79 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Graduation + CAT/NMET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CAT, XAT, GMAT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>22 Oct - 28 Feb 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BBA</t>
+          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,17 +826,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>12.9 Lakhs</t>
+          <t>12.9 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10+2 + CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 Dec - 27 Dec 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M.Phil/Ph.D in Law</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.34 Lakhs</t>
+          <t>3.34 L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Post Graduation +UGC NET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Sept 2025</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BBA</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.3 Lakhs</t>
+          <t>22.3 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10+2 + NMET/IPMAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>30 Nov - 31 May 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1002,32 +1002,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>Certificate Course in Cyber Law</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>Certificate Course in Cyber Law</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>₹65000</t>
+          <t>7,500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Library Fees</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Library Fees</t>
+          <t>Master of Laws [L.L.M] + Ph.D</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Library Fees</t>
+          <t>Master of Laws [L.L.M] + Ph.D</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>₹13000</t>
+          <t>1.04 L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 Dec - 27 Dec 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Room Rent</t>
+          <t>Advance Diploma in Global Financial Market</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Room Rent</t>
+          <t>Advance Diploma in Global Financial Market</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Room Rent</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>₹67000</t>
+          <t>33,000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1188,32 +1188,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Onetime Payment</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Onetime Payment</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Onetime Payment</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>₹10000</t>
+          <t>89,000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Full Time</t>
+          <t>Part Time</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Sept 2025</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Refundable Deposit</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Refundable Deposit</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Refundable Deposit</t>
+          <t>Master of Laws [L.L.M]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>₹20000</t>
+          <t>1.75 Lakhs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>LLB + CLAT-PG</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT PG</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>MBA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>₹175000</t>
+          <t>8.79 Lakhs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + CAT/NMET</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CAT, XAT, GMAT</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Intellectual Property Rights</t>
+          <t>BBA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Intellectual Property Rights</t>
+          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Intellectual Property Rights</t>
+          <t>Bachelor of Arts + Bachelor of Laws [BALLB] {Hons.}</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>₹ 1.75 Lakhs</t>
+          <t>12.9 Lakhs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>LLB + CLAT-PG</t>
+          <t>10+2 + CLAT</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1436,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>International Trade Law</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>International Trade Law</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>International Trade Law</t>
+          <t>M.Phil/Ph.D in Law</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>₹ 1.75 Lakhs</t>
+          <t>3.34 Lakhs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>LLB + CLAT-PG</t>
+          <t>Post Graduation +UGC NET</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1498,27 +1498,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Corporate And Commercial Law</t>
+          <t>BBA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Corporate And Commercial Law</t>
+          <t>Bachelor of Business Administration [BBA] + Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Corporate And Commercial Law</t>
+          <t>Bachelor of Business Administration [BBA] + Master of Business Administration [MBA]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>₹ 1.75 Lakhs</t>
+          <t>22.3 Lakhs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>5 Years</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>LLB + CLAT-PG</t>
+          <t>10+2 + NMET/IPMAT</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1560,17 +1560,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Criminal Law</t>
+          <t>Intellectual Property Rights</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Criminal Law</t>
+          <t>Intellectual Property Rights</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Criminal Law</t>
+          <t>Intellectual Property Rights</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3-5 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CLAT</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Environmental Law</t>
+          <t>International Trade Law</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Environmental Law</t>
+          <t>International Trade Law</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Environmental Law</t>
+          <t>International Trade Law</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1684,17 +1684,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Family Law</t>
+          <t>Corporate And Commercial Law</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Family Law</t>
+          <t>Corporate And Commercial Law</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Family Law</t>
+          <t>Corporate And Commercial Law</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1746,22 +1746,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Insolvency &amp; Bankruptcy Law</t>
+          <t>Criminal Law</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Insolvency &amp; Bankruptcy Law</t>
+          <t>Criminal Law</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Insolvency &amp; Bankruptcy Law</t>
+          <t>Criminal Law</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>₹ 3.2 Lakhs</t>
+          <t>₹ 1.75 Lakhs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1808,17 +1808,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Legal Pedagogy And Research</t>
+          <t>Environmental Law</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Legal Pedagogy And Research</t>
+          <t>Environmental Law</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Legal Pedagogy And Research</t>
+          <t>Environmental Law</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Legal Theory</t>
+          <t>Family Law</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Legal Theory</t>
+          <t>Family Law</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Legal Theory</t>
+          <t>Family Law</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1932,27 +1932,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>Insolvency &amp; Bankruptcy Law</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>Insolvency &amp; Bankruptcy Law</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>Insolvency &amp; Bankruptcy Law</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>₹220000</t>
+          <t>₹ 3.2 Lakhs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>LLB + CLAT-PG</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CLAT</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1994,22 +1994,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Library Fees</t>
+          <t>Legal Pedagogy And Research</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Library Fees</t>
+          <t>Legal Pedagogy And Research</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Library Fees</t>
+          <t>Legal Pedagogy And Research</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>₹100000</t>
+          <t>₹ 1.75 Lakhs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>LLB + CLAT-PG</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Room Rent</t>
+          <t>Legal Theory</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Room Rent</t>
+          <t>Legal Theory</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Room Rent</t>
+          <t>Legal Theory</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>₹107000</t>
+          <t>₹ 1.75 Lakhs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>LLB + CLAT-PG</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2118,22 +2118,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hostel Deposit</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hostel Deposit</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hostel Deposit</t>
+          <t>Management</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>₹10000</t>
+          <t>₹ 3.34 Lakhs</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Post Graduation +UGC NET</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2180,27 +2180,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Library Deposit</t>
+          <t>L.L.M + Ph.D</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Library Deposit</t>
+          <t>L.L.M + Ph.D (General)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Library Deposit</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>₹5000</t>
+          <t>L.L.B.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 Years</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2242,29 +2242,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mess Deposit</t>
+          <t>Diploma</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mess Deposit</t>
+          <t>Diploma (General)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mess Deposit</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>₹5000</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
+          <t>Graduation</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2272,7 +2268,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>₹ 33,000</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2304,29 +2300,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Library Fee</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Library Fee</t>
+          <t>Certification (General)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Library Fee</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
+          <t>10+2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2334,7 +2326,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>₹ 7,500</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2353,618 +2345,6 @@
         </is>
       </c>
       <c r="L28" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Yearly Fees</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Yearly Fees</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Yearly Fees</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>₹447000</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Tuition Fee</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>₹ 8.5 Lakhs</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Total Fee</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>₹ 12.9 Lakhs</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Total Fees (2026 - 2027)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Total Fees (2026 - 2027)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Total Fees (2026 - 2027)</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>₹3.34 Lakhs</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Management</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>₹ 3.34 Lakhs</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2 Years</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Post Graduation +UGC NET</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>PG</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Tuition Fees</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tuition Fees</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Tuition Fees</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>₹225000</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Yearly Fees</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Yearly Fees</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Yearly Fees</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>₹452000</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>L.L.M + Ph.D</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>L.L.M + Ph.D (General)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>L.L.B.</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>3-5 Years</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>GATE / UGC NET</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Doctorate</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Diploma</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Diploma (General)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Graduation</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>₹ 33,000</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>25366</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Certification</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Certification (General)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>10+2</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>₹ 7,500</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
@@ -3118,12 +2498,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19,00,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3158,7 +2538,7 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3197,7 +2577,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CD Rank #12</t>
+          <t>#2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
